--- a/rules/CORE-002051/positive/01/data/CORE-002051-positive-01.xlsx
+++ b/rules/CORE-002051/positive/01/data/CORE-002051-positive-01.xlsx
@@ -650,13 +650,13 @@
         <v/>
       </c>
       <c r="E5" s="6" t="str">
-        <v>CTAUG</v>
+        <v>FDATCHSP</v>
       </c>
       <c r="F5" s="6" t="str">
-        <v>CDISC Therapeutic Area User Guide</v>
+        <v>FDA Technical Specification Response</v>
       </c>
       <c r="G5" s="6" t="str">
-        <v>Tuberculosis Therapeutic Area User Guide v2.0</v>
+        <v>Study Data Technical Conformance Guide v4.2.1</v>
       </c>
       <c r="H5" s="6" t="str">
         <v>NA</v>
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="K5" s="6" t="str">
-        <v/>
+        <v>2025-03-28</v>
       </c>
     </row>
   </sheetData>
